--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -2434,20 +2434,20 @@
       <c r="E21" s="2" t="inlineStr"/>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>Dropdown list: 1-8 or more</t>
+          <t>1=1 2=2 3=3 4=4 5=5 6=6 7=7 8=7+</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>Numeric</t>
+          <t>Categorical (Nominal)</t>
         </is>
       </c>
       <c r="H21" s="2" t="n">
-        <v>59.64</v>
+        <v>88.98999999999999</v>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2470,11 +2470,11 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>Clarity</t>
+          <t>Clarity, Response Categories</t>
         </is>
       </c>
       <c r="O21" s="2" t="n">
-        <v>0.164</v>
+        <v>0.189</v>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
@@ -2514,20 +2514,20 @@
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>Dropdown list: 1-8 or more</t>
+          <t>1=1 2=2 3=3 4=4 5=5 6=6 7=7 8=7+</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>Numeric</t>
+          <t>Categorical (Nominal)</t>
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>61.45</v>
+        <v>91.33</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2550,11 +2550,11 @@
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>Clarity</t>
+          <t>Clarity, Response Categories</t>
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>0.16</v>
+        <v>0.184</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
@@ -5369,7 +5369,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>32; 31</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -5423,7 +5423,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>32; 31</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -5477,7 +5477,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>32; 31</t>
+          <t>31</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -3874,10 +3874,14 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr"/>
+          <t>Follow-up Question</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
           <t>1=Yes 2=No 3=Prefer not to say</t>
@@ -3888,51 +3892,25 @@
           <t>Categorical (Nominal)</t>
         </is>
       </c>
-      <c r="H14" s="2" t="n">
-        <v>38.59</v>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="n">
-        <v>0.123</v>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="2" t="inlineStr"/>
+      <c r="J14" s="2" t="inlineStr"/>
+      <c r="K14" s="2" t="inlineStr"/>
+      <c r="L14" s="2" t="inlineStr"/>
+      <c r="M14" s="2" t="inlineStr"/>
+      <c r="N14" s="2" t="inlineStr"/>
+      <c r="O14" s="2" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>If any of the disabilities above are selected</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr"/>
+          <t>Display if any option other than "I do not have a disability" is selected for "Do you have a disability or disabilities from any of the following categories?"</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>Display if any option other than "I do not have a disability" is selected for "Do you have a disability or disabilities from any of the following categories?"</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n">

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -3903,12 +3903,12 @@
       <c r="P14" s="2" t="inlineStr"/>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Display if any option other than "I do not have a disability" is selected for "Do you have a disability or disabilities from any of the following categories?"</t>
+          <t>Display if "Prefer not to respond" and "I do not have a disability" are not selected for "Do you have a disability or disabilities from any of the following categories?"</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Display if any option other than "I do not have a disability" is selected for "Do you have a disability or disabilities from any of the following categories?"</t>
+          <t>Display if "Prefer not to respond" and "I do not have a disability" are not selected for "Do you have a disability or disabilities from any of the following categories?"</t>
         </is>
       </c>
     </row>
@@ -4794,10 +4794,14 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr"/>
+          <t>Follow-up Question</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
           <t>6=Very satisfied 5=Satisfied 4=Somewhat satisfied 3=Somewhat dissatisfied 2=Dissatisfied 1=Very dissatisfied</t>
@@ -4808,51 +4812,25 @@
           <t>Matrix</t>
         </is>
       </c>
-      <c r="H29" s="2" t="n">
-        <v>26.69</v>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K29" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="L29" s="2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="M29" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N29" s="2" t="inlineStr">
-        <is>
-          <t>Knowledge/Memory, Reading</t>
-        </is>
-      </c>
-      <c r="O29" s="2" t="n">
-        <v>0.513</v>
-      </c>
-      <c r="P29" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="2" t="inlineStr"/>
+      <c r="J29" s="2" t="inlineStr"/>
+      <c r="K29" s="2" t="inlineStr"/>
+      <c r="L29" s="2" t="inlineStr"/>
+      <c r="M29" s="2" t="inlineStr"/>
+      <c r="N29" s="2" t="inlineStr"/>
+      <c r="O29" s="2" t="inlineStr"/>
+      <c r="P29" s="2" t="inlineStr"/>
       <c r="Q29" s="2" t="inlineStr">
         <is>
-          <t>One matrix table question with 6 statements for each option selected for “From which of the following places did you receive counseling or therapy?” (Up to 8)</t>
-        </is>
-      </c>
-      <c r="R29" s="2" t="inlineStr"/>
+          <t>Display only if "Have you ever received counseling or therapy for mental health concerns?" is not "No, Never." One matrix table question with 6 statements for each option selected for "From which of the following places did you receive counseling or therapy?" (Up to 8)</t>
+        </is>
+      </c>
+      <c r="R29" s="2" t="inlineStr">
+        <is>
+          <t>Display only if "Have you ever received counseling or therapy for mental health concerns?" is not "No, Never." One matrix table question with 6 statements for each option selected for "From which of the following places did you receive counseling or therapy?" (Up to 8)</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="n">
@@ -5504,10 +5482,14 @@
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="inlineStr"/>
+          <t>Follow-up Question</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
       <c r="F41" s="2" t="inlineStr">
         <is>
           <t>1=It has not impaired my academic performance 2=It has minimally impaired my academic performance 3=It has moderately impaired my academic performance 4=It has significantly impaired my academic performance</t>
@@ -5518,53 +5500,23 @@
           <t>Categorical (Nominal)</t>
         </is>
       </c>
-      <c r="H41" s="2" t="n">
-        <v>4.14</v>
-      </c>
-      <c r="I41" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J41" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K41" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N41" s="2" t="inlineStr">
-        <is>
-          <t>Response Categories</t>
-        </is>
-      </c>
-      <c r="O41" s="2" t="n">
-        <v>0.425</v>
-      </c>
-      <c r="P41" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr"/>
+      <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>Display if “1=Attention deficit hyperactivity disorder (ADHD or ADD)” is selected for “Specifically,</t>
+          <t>Display if "1=Attention deficit hyperactivity disorder (ADHD or ADD)" is selected for "Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)"</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>Display if “1=Attention deficit hyperactivity disorder (ADHD or ADD)” is selected for “Specifically,</t>
+          <t>Display if "1=Attention deficit hyperactivity disorder (ADHD or ADD)" is selected for "Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)"</t>
         </is>
       </c>
     </row>
@@ -6013,12 +5965,12 @@
       <c r="P48" s="2" t="inlineStr"/>
       <c r="Q48" s="2" t="inlineStr">
         <is>
-          <t>Display if any option other than “8=No, none of these” is selected for “In the past 12 months, have you received support for your mental or emotional health from any of the following sources?”</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months, have you received support for your mental or emotional health from any of the following sources?"</t>
         </is>
       </c>
       <c r="R48" s="2" t="inlineStr">
         <is>
-          <t>Display if any option other than “8=No, none of these” is selected for “In the past 12 months, have you received support for your mental or emotional health from any of the following sources?”</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months, have you received support for your mental or emotional health from any of the following sources?"</t>
         </is>
       </c>
     </row>
@@ -6349,12 +6301,12 @@
       <c r="P53" s="2" t="inlineStr"/>
       <c r="Q53" s="2" t="inlineStr">
         <is>
-          <t>Display if any option other than “1=I do not have any health insurance coverage” is selected for “What is the source of your current health insurance coverage?”</t>
+          <t>Display if "1=I do not have any health insurance coverage" is not selected for "What is the source of your current health insurance coverage?"</t>
         </is>
       </c>
       <c r="R53" s="2" t="inlineStr">
         <is>
-          <t>Display if any option other than “1=I do not have any health insurance coverage” is selected for “What is the source of your current health insurance coverage?”</t>
+          <t>Display if "1=I do not have any health insurance coverage" is not selected for "What is the source of your current health insurance coverage?"</t>
         </is>
       </c>
     </row>
@@ -6403,12 +6355,12 @@
       <c r="P54" s="2" t="inlineStr"/>
       <c r="Q54" s="2" t="inlineStr">
         <is>
-          <t>Display if any option other than “1=I do not have any health insurance coverage” is selected for “What is the source of your current health insurance coverage?”</t>
+          <t>Display if "1=I do not have any health insurance coverage" is not selected for "What is the source of your current health insurance coverage?"</t>
         </is>
       </c>
       <c r="R54" s="2" t="inlineStr">
         <is>
-          <t>Display if any option other than “1=I do not have any health insurance coverage” is selected for “What is the source of your current health insurance coverage?”</t>
+          <t>Display if "1=I do not have any health insurance coverage" is not selected for "What is the source of your current health insurance coverage?"</t>
         </is>
       </c>
     </row>

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -5438,7 +5438,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1=YourDost 2=Urgent Care or the Emergency Room 3=Provider in the local community (not on campus) 4=Provider in my hometown 5=Provider affiliated with a telehealth company 6=Others</t>
+          <t>1=YourDost 2=Urgent Care or the Emergency Room 3=Provider in the local community (not on campus) 4=Provider in my hometown 5=Provider affiliated with a telehealth company 6=Other (please specify)</t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>7; 12</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       <c r="P41" s="2" t="inlineStr"/>
       <c r="Q41" s="2" t="inlineStr">
         <is>
-          <t>Display if "1=Attention deficit hyperactivity disorder (ADHD or ADD)" is selected for "Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)"</t>
+          <t>Display if "1=Attention deficit hyperactivity disorder (ADHD or ADD)" is selected for "Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)" or "1=Attention deficit/hyperactivity disorders" is selected for "Do you have a disability or disabilities from any of the following categories?"</t>
         </is>
       </c>
       <c r="R41" s="2" t="inlineStr">
         <is>
-          <t>Display if "1=Attention deficit hyperactivity disorder (ADHD or ADD)" is selected for "Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)"</t>
+          <t>Display if "1=Attention deficit hyperactivity disorder (ADHD or ADD)" is selected for "Specifically, which of the following neurodevelopmental disorder or intellectual disability were you diagnosed with by a professional? (Select all that apply)" or "1=Attention deficit/hyperactivity disorders" is selected for "Do you have a disability or disabilities from any of the following categories?"</t>
         </is>
       </c>
     </row>

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -22,13 +22,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="5">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -60,7 +63,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -68,18 +71,24 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5244,10 +5253,14 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr"/>
+          <t>Follow-up Question</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
           <t>1=Psychostimulants (methylphenidate (Ritalin, or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health (please specify) 8=None of the above [mutually exclusive]</t>
@@ -5258,51 +5271,25 @@
           <t>Categorical (Nominal)</t>
         </is>
       </c>
-      <c r="H37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J37" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K37" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L37" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N37" s="2" t="inlineStr">
-        <is>
-          <t>Response Categories</t>
-        </is>
-      </c>
-      <c r="O37" s="2" t="n">
-        <v>0.433</v>
-      </c>
-      <c r="P37" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
+      <c r="H37" s="2" t="inlineStr"/>
+      <c r="I37" s="2" t="inlineStr"/>
+      <c r="J37" s="2" t="inlineStr"/>
+      <c r="K37" s="2" t="inlineStr"/>
+      <c r="L37" s="2" t="inlineStr"/>
+      <c r="M37" s="2" t="inlineStr"/>
+      <c r="N37" s="2" t="inlineStr"/>
+      <c r="O37" s="2" t="inlineStr"/>
+      <c r="P37" s="2" t="inlineStr"/>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
-        </is>
-      </c>
-      <c r="R37" s="2" t="inlineStr"/>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+        </is>
+      </c>
+      <c r="R37" s="2" t="inlineStr">
+        <is>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n">
@@ -5536,10 +5523,14 @@
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="inlineStr"/>
+          <t>Follow-up Question</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>31</t>
+        </is>
+      </c>
       <c r="F42" s="2" t="inlineStr">
         <is>
           <t>1=Less than 1 month 2=Between 1 and 2 months 3=2 months or more 4=Did not take</t>
@@ -5550,51 +5541,25 @@
           <t>Categorical (Ordinal)</t>
         </is>
       </c>
-      <c r="H42" s="2" t="n">
-        <v>84.01000000000001</v>
-      </c>
-      <c r="I42" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J42" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K42" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L42" s="2" t="n">
-        <v>0.08</v>
-      </c>
-      <c r="M42" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N42" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O42" s="2" t="n">
-        <v>0.182</v>
-      </c>
-      <c r="P42" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
+      <c r="H42" s="2" t="inlineStr"/>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+      <c r="K42" s="2" t="inlineStr"/>
+      <c r="L42" s="2" t="inlineStr"/>
+      <c r="M42" s="2" t="inlineStr"/>
+      <c r="N42" s="2" t="inlineStr"/>
+      <c r="O42" s="2" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr"/>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
-        </is>
-      </c>
-      <c r="R42" s="2" t="inlineStr"/>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+        </is>
+      </c>
+      <c r="R42" s="2" t="inlineStr">
+        <is>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n">

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -13,6 +13,7 @@
     <sheet name="Overall Health" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Academic Persistence, Retention" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Financial Stress" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Sheet1" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -883,7 +884,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>127</t>
+          <t>137</t>
         </is>
       </c>
     </row>
@@ -8839,6 +8840,842 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:R11"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="16" customWidth="1" min="1" max="1"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="55" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="4" max="4"/>
+    <col width="16" customWidth="1" min="5" max="5"/>
+    <col width="40" customWidth="1" min="6" max="6"/>
+    <col width="16" customWidth="1" min="7" max="7"/>
+    <col width="16" customWidth="1" min="8" max="8"/>
+    <col width="16" customWidth="1" min="9" max="9"/>
+    <col width="16" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="16" customWidth="1" min="12" max="12"/>
+    <col width="16" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="16" customWidth="1" min="15" max="15"/>
+    <col width="16" customWidth="1" min="16" max="16"/>
+    <col width="40" customWidth="1" min="17" max="17"/>
+    <col width="40" customWidth="1" min="18" max="18"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>Question #</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>Section</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>Question</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>Question Role</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>Parent Question #</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>Response Categories</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>Response Type</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>Flesch Reading Ease</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>FRE Band</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>Blooms Score</t>
+        </is>
+      </c>
+      <c r="K1" s="4" t="inlineStr">
+        <is>
+          <t>Response Option Complexity</t>
+        </is>
+      </c>
+      <c r="L1" s="4" t="inlineStr">
+        <is>
+          <t>Response Option Complexity Score</t>
+        </is>
+      </c>
+      <c r="M1" s="4" t="inlineStr">
+        <is>
+          <t>Time-span and Sensitivity</t>
+        </is>
+      </c>
+      <c r="N1" s="4" t="inlineStr">
+        <is>
+          <t>QAS problems</t>
+        </is>
+      </c>
+      <c r="O1" s="4" t="inlineStr">
+        <is>
+          <t>Cognitive Load Score</t>
+        </is>
+      </c>
+      <c r="P1" s="4" t="inlineStr">
+        <is>
+          <t>Cognitive Load Band</t>
+        </is>
+      </c>
+      <c r="Q1" s="4" t="inlineStr">
+        <is>
+          <t>Notes</t>
+        </is>
+      </c>
+      <c r="R1" s="4" t="inlineStr">
+        <is>
+          <t>Skip/Display Logic</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>Socioeconomic status</t>
+        </is>
+      </c>
+      <c r="C2" s="2" t="inlineStr">
+        <is>
+          <t>How would you describe your financial situation while growing up?</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="inlineStr"/>
+      <c r="F2" s="2" t="inlineStr">
+        <is>
+          <t>1=Always stressful 2=Often stressful 3=Sometimes stressful 4=Rarely stressful 5=Never stressful</t>
+        </is>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>Likert (5-point)</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="n">
+        <v>30.02</v>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K2" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M2" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N2" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O2" s="2" t="n">
+        <v>0.165</v>
+      </c>
+      <c r="P2" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q2" s="2" t="inlineStr">
+        <is>
+          <t>CCMH Standardized Data Set</t>
+        </is>
+      </c>
+      <c r="R2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Socioeconomic status</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>How would you describe your financial situation right now?</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr"/>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>1=Always stressful 2=Often stressful 3=Sometimes stressful 4=Rarely stressful 5=Never stressful</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Likert (5-point)</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="n">
+        <v>34.42</v>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K3" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M3" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N3" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O3" s="2" t="n">
+        <v>0.156</v>
+      </c>
+      <c r="P3" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q3" s="2" t="inlineStr">
+        <is>
+          <t>CCMH Standardized Data Set</t>
+        </is>
+      </c>
+      <c r="R3" s="2" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>Socioeconomic status</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>Within the past 12 months I worried whether our food would run out before we got money to buy more.</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr"/>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1=Often true 2=Sometimes true 3=Never true</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>Categorical (Ordinal)</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="n">
+        <v>76.59</v>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>0.117</v>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>Clarity, Knowledge/Memory</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>0.363</v>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr"/>
+      <c r="R4" s="2" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Socioeconomic status</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Within the past 12 months the food I bought just didn’t last and I didn’t have money to get more.</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr"/>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>1=Often true 2=Sometimes true 3=Never true</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Categorical (Ordinal)</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="n">
+        <v>87.94</v>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>Clarity, Knowledge/Memory</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr"/>
+      <c r="R5" s="2" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Socioeconomic status</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Within the past 12 months, which of the following expenses have you had difficulty paying for? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>1=School 2=Food 3=Transportation 4=Childcare 5=Health care 6=Textbooks or course materials 7=Housing 8=None of the above [mutually exclusive]</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="n">
+        <v>49.47</v>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>Knowledge/Memory, Response Categories</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>0.418</v>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr"/>
+      <c r="R6" s="2" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Housing concerns</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Do you have any concerns about your current living situation, like housing conditions, safety, and costs?</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Mother Question</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr"/>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>1=Yes 2=No</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="n">
+        <v>50.35</v>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>None</t>
+        </is>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>0.099</v>
+      </c>
+      <c r="P7" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
+      <c r="R7" s="2" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Housing concerns</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>What are those concerns? (Select all that apply.</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Follow-up Question</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>1=Condition/quality of housing 2=Lack of more permanent housing 3=Ability to pay for housing or utilities 4=Feeling safe 5=Other (please specify)</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr"/>
+      <c r="J8" s="2" t="inlineStr"/>
+      <c r="K8" s="2" t="inlineStr"/>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="2" t="inlineStr"/>
+      <c r="N8" s="2" t="inlineStr"/>
+      <c r="O8" s="2" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr"/>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>Display if “Yes” is selected for “Do you have any concerns about your current living situation, like housing conditions, safety, and costs?”</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>Display if “Yes” is selected for “Do you have any concerns about your current living situation, like housing conditions, safety, and costs?”</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Housing concerns</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Which of the following have you used to pay for educational expenses (room, board, tuition, and fees)? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr"/>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>1=Family resources (parents, relatives, spouse, etc.) 2=Your own resources (income from work, work-study, etc.) 3=Aid that need not be repaid (grants, scholarships, military, etc.) 4=Aid that must be repaid (loans) 5=Other sources (please specify)</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="n">
+        <v>57</v>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>Response Categories</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>0.169</v>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr"/>
+      <c r="R9" s="2" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Financing education</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>To what extent do you agree or disagree with the following statements? I am worried about my ability to pay for school. I am worried about my ability to repay my student loans in the future [if loans selected above] My student loans negatively impact my mental health [if loans selected above]</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr"/>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>Likert (6-point)</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n">
+        <v>43.41</v>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Moderate</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>Clarity, Reading, Response Categories, Sensitivity/Bias</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>0.597</v>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="R10" s="2" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Scholarship Status</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Do you receive scholarship funding from your institution? (Select all that apply)</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Independent Question</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr"/>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>1=No [mutually exclusive] 2=Yes, a need based scholarship 3=Yes, an academic scholarship (or merit scholarship) 4=Yes, an athletic scholarship 5=Other (please specify)</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>Categorical (Nominal)</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n">
+        <v>31.88</v>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>Response Categories</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr"/>
+      <c r="R11" s="2" t="inlineStr"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -8960,7 +9797,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -9036,7 +9873,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9112,7 +9949,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9184,7 +10021,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -9256,7 +10093,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -9751,7 +10588,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>How often have you used online sportsbook applications (e.g., Draftkings, Fanduel, Bet MGM) in the past year in order to participate in sports betting?</t>
+          <t>How often have you used online sportsbook applications (e.g., Dream11,Parimatch,Dafabet) in the past year in order to participate in sports betting?</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -9805,7 +10642,7 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>To what extent to which you agree or disagree with each of the following statements: I feel like sports betting controls my life I have no problem setting limits on how much money I bet on sports</t>
+          <t>To what extent to which you agree or disagree with each of the following statements:I feel like sports betting controls my life. I have no problem setting limits on how much money I bet on sports.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -9820,7 +10657,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Neither agree nor disagree 5=Somewhat disagree 6=Disagree 7=Strongly disagree</t>
+          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -13,7 +13,6 @@
     <sheet name="Overall Health" sheetId="4" state="visible" r:id="rId4"/>
     <sheet name="Academic Persistence, Retention" sheetId="5" state="visible" r:id="rId5"/>
     <sheet name="Financial Stress" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Sheet1" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -884,7 +883,7 @@
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>137</t>
+          <t>127</t>
         </is>
       </c>
     </row>
@@ -8840,842 +8839,6 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R11"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="16" customWidth="1" min="1" max="1"/>
-    <col width="16" customWidth="1" min="2" max="2"/>
-    <col width="55" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="16" customWidth="1" min="5" max="5"/>
-    <col width="40" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="16" customWidth="1" min="8" max="8"/>
-    <col width="16" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="16" customWidth="1" min="11" max="11"/>
-    <col width="16" customWidth="1" min="12" max="12"/>
-    <col width="16" customWidth="1" min="13" max="13"/>
-    <col width="22" customWidth="1" min="14" max="14"/>
-    <col width="16" customWidth="1" min="15" max="15"/>
-    <col width="16" customWidth="1" min="16" max="16"/>
-    <col width="40" customWidth="1" min="17" max="17"/>
-    <col width="40" customWidth="1" min="18" max="18"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="4" t="inlineStr">
-        <is>
-          <t>Question #</t>
-        </is>
-      </c>
-      <c r="B1" s="4" t="inlineStr">
-        <is>
-          <t>Section</t>
-        </is>
-      </c>
-      <c r="C1" s="4" t="inlineStr">
-        <is>
-          <t>Question</t>
-        </is>
-      </c>
-      <c r="D1" s="4" t="inlineStr">
-        <is>
-          <t>Question Role</t>
-        </is>
-      </c>
-      <c r="E1" s="4" t="inlineStr">
-        <is>
-          <t>Parent Question #</t>
-        </is>
-      </c>
-      <c r="F1" s="4" t="inlineStr">
-        <is>
-          <t>Response Categories</t>
-        </is>
-      </c>
-      <c r="G1" s="4" t="inlineStr">
-        <is>
-          <t>Response Type</t>
-        </is>
-      </c>
-      <c r="H1" s="4" t="inlineStr">
-        <is>
-          <t>Flesch Reading Ease</t>
-        </is>
-      </c>
-      <c r="I1" s="4" t="inlineStr">
-        <is>
-          <t>FRE Band</t>
-        </is>
-      </c>
-      <c r="J1" s="4" t="inlineStr">
-        <is>
-          <t>Blooms Score</t>
-        </is>
-      </c>
-      <c r="K1" s="4" t="inlineStr">
-        <is>
-          <t>Response Option Complexity</t>
-        </is>
-      </c>
-      <c r="L1" s="4" t="inlineStr">
-        <is>
-          <t>Response Option Complexity Score</t>
-        </is>
-      </c>
-      <c r="M1" s="4" t="inlineStr">
-        <is>
-          <t>Time-span and Sensitivity</t>
-        </is>
-      </c>
-      <c r="N1" s="4" t="inlineStr">
-        <is>
-          <t>QAS problems</t>
-        </is>
-      </c>
-      <c r="O1" s="4" t="inlineStr">
-        <is>
-          <t>Cognitive Load Score</t>
-        </is>
-      </c>
-      <c r="P1" s="4" t="inlineStr">
-        <is>
-          <t>Cognitive Load Band</t>
-        </is>
-      </c>
-      <c r="Q1" s="4" t="inlineStr">
-        <is>
-          <t>Notes</t>
-        </is>
-      </c>
-      <c r="R1" s="4" t="inlineStr">
-        <is>
-          <t>Skip/Display Logic</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>Socioeconomic status</t>
-        </is>
-      </c>
-      <c r="C2" s="2" t="inlineStr">
-        <is>
-          <t>How would you describe your financial situation while growing up?</t>
-        </is>
-      </c>
-      <c r="D2" s="2" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="inlineStr"/>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>1=Always stressful 2=Often stressful 3=Sometimes stressful 4=Rarely stressful 5=Never stressful</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>Likert (5-point)</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>30.02</v>
-      </c>
-      <c r="I2" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J2" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K2" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L2" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M2" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N2" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O2" s="2" t="n">
-        <v>0.165</v>
-      </c>
-      <c r="P2" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="Q2" s="2" t="inlineStr">
-        <is>
-          <t>CCMH Standardized Data Set</t>
-        </is>
-      </c>
-      <c r="R2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="B3" s="2" t="inlineStr">
-        <is>
-          <t>Socioeconomic status</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>How would you describe your financial situation right now?</t>
-        </is>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr"/>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>1=Always stressful 2=Often stressful 3=Sometimes stressful 4=Rarely stressful 5=Never stressful</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
-          <t>Likert (5-point)</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>34.42</v>
-      </c>
-      <c r="I3" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J3" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="K3" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M3" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N3" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O3" s="2" t="n">
-        <v>0.156</v>
-      </c>
-      <c r="P3" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="Q3" s="2" t="inlineStr">
-        <is>
-          <t>CCMH Standardized Data Set</t>
-        </is>
-      </c>
-      <c r="R3" s="2" t="inlineStr"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Socioeconomic status</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>Within the past 12 months I worried whether our food would run out before we got money to buy more.</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr"/>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>1=Often true 2=Sometimes true 3=Never true</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>Categorical (Ordinal)</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>76.59</v>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="n">
-        <v>0.117</v>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>Clarity, Knowledge/Memory</t>
-        </is>
-      </c>
-      <c r="O4" s="2" t="n">
-        <v>0.363</v>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr"/>
-      <c r="R4" s="2" t="inlineStr"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Socioeconomic status</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>Within the past 12 months the food I bought just didn’t last and I didn’t have money to get more.</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr"/>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1=Often true 2=Sometimes true 3=Never true</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>Categorical (Ordinal)</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>87.94</v>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>Clarity, Knowledge/Memory</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="n">
-        <v>0.341</v>
-      </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr"/>
-      <c r="R5" s="2" t="inlineStr"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Socioeconomic status</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Within the past 12 months, which of the following expenses have you had difficulty paying for? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1=School 2=Food 3=Transportation 4=Childcare 5=Health care 6=Textbooks or course materials 7=Housing 8=None of the above [mutually exclusive]</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>49.47</v>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K6" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
-        <is>
-          <t>Knowledge/Memory, Response Categories</t>
-        </is>
-      </c>
-      <c r="O6" s="2" t="n">
-        <v>0.418</v>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr"/>
-      <c r="R6" s="2" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="n">
-        <v>6</v>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Housing concerns</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Do you have any concerns about your current living situation, like housing conditions, safety, and costs?</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>Mother Question</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr"/>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>1=Yes 2=No</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>50.35</v>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K7" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M7" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N7" s="2" t="inlineStr">
-        <is>
-          <t>None</t>
-        </is>
-      </c>
-      <c r="O7" s="2" t="n">
-        <v>0.099</v>
-      </c>
-      <c r="P7" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="Q7" s="2" t="inlineStr"/>
-      <c r="R7" s="2" t="inlineStr"/>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="n">
-        <v>7</v>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Housing concerns</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>What are those concerns? (Select all that apply.</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Follow-up Question</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1=Condition/quality of housing 2=Lack of more permanent housing 3=Ability to pay for housing or utilities 4=Feeling safe 5=Other (please specify)</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="2" t="inlineStr"/>
-      <c r="J8" s="2" t="inlineStr"/>
-      <c r="K8" s="2" t="inlineStr"/>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="2" t="inlineStr"/>
-      <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr"/>
-      <c r="P8" s="2" t="inlineStr"/>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>Display if “Yes” is selected for “Do you have any concerns about your current living situation, like housing conditions, safety, and costs?”</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>Display if “Yes” is selected for “Do you have any concerns about your current living situation, like housing conditions, safety, and costs?”</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="n">
-        <v>8</v>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Housing concerns</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>Which of the following have you used to pay for educational expenses (room, board, tuition, and fees)? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr"/>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1=Family resources (parents, relatives, spouse, etc.) 2=Your own resources (income from work, work-study, etc.) 3=Aid that need not be repaid (grants, scholarships, military, etc.) 4=Aid that must be repaid (loans) 5=Other sources (please specify)</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>57</v>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>Response Categories</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="n">
-        <v>0.169</v>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr"/>
-      <c r="R9" s="2" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="n">
-        <v>9</v>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>Financing education</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>To what extent do you agree or disagree with the following statements? I am worried about my ability to pay for school. I am worried about my ability to repay my student loans in the future [if loans selected above] My student loans negatively impact my mental health [if loans selected above]</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr"/>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>Likert (6-point)</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="n">
-        <v>43.41</v>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>Moderate</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>Clarity, Reading, Response Categories, Sensitivity/Bias</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="n">
-        <v>0.597</v>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr"/>
-      <c r="R10" s="2" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="n">
-        <v>10</v>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>Scholarship Status</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>Do you receive scholarship funding from your institution? (Select all that apply)</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Independent Question</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr"/>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>1=No [mutually exclusive] 2=Yes, a need based scholarship 3=Yes, an academic scholarship (or merit scholarship) 4=Yes, an athletic scholarship 5=Other (please specify)</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>Categorical (Nominal)</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="n">
-        <v>31.88</v>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>Response Categories</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="n">
-        <v>0.22</v>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr"/>
-      <c r="R11" s="2" t="inlineStr"/>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
   <dimension ref="A1:R14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -5282,12 +5282,12 @@
       <c r="P37" s="2" t="inlineStr"/>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
     </row>
@@ -5552,12 +5552,12 @@
       <c r="P42" s="2" t="inlineStr"/>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?” Display if “8=No, none of these” is not selected for “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
     </row>
@@ -8960,7 +8960,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic status</t>
+          <t>Socioeconom ic status</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -9036,7 +9036,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic status</t>
+          <t>Socioeconom ic status</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic status</t>
+          <t>Socioeconom ic status</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9184,7 +9184,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic status</t>
+          <t>Socioeconom ic status</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Socioeconomic status</t>
+          <t>Socioeconom ic status</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -9751,7 +9751,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>How often have you used online sportsbook applications (e.g., Dream11,Parimatch,Dafabet) in the past year in order to participate in sports betting?</t>
+          <t>How often have you used online sportsbook applications (e.g., Draftkings, Fanduel, Bet MGM) in the past year in order to participate in sports betting?</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
@@ -9805,7 +9805,9 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>To what extent to which you agree or disagree with each of the following statements:I feel like sports betting controls my life. I have no problem setting limits on how much money I bet on sports.</t>
+          <t>To what extent to which you agree or disagree with each of the following statements:
+1. I feel like sports betting controls my life.
+2. I have no problem setting limits on how much money I bet on sports.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
@@ -9820,7 +9822,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Somewhat disagree 5=Disagree 6=Strongly disagree</t>
+          <t>1=Strongly agree 2=Agree 3=Somewhat agree 4=Neither agree nor disagree 5=Somewhat disagree 6=Disagree 7=Strongly disagree</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -2787,7 +2787,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1=An official institutional communication (e.g., email, emergency alert system) 2=A memorial 3=News media (e.g., newspapers or blogs) 4=Social media (e.g., Reddit, Instagram, Meta, X) 5=Word of mouth from my peers 6=Other (please specify) 7=I don’t remember 8=None of these</t>
+          <t>1=An official institutional communication (e.g., email, emergency alert system) 2=A memorial 3=News media (e.g., newspapers or blogs) 4=Social media (e.g., Reddit, Instagram, Meta, X) 5=Word of mouth from my peers 6=Others  7=I don’t remember 8=None of these</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1=Major depressive disorder 2=Dysthymia or persistent depressive disorder 3=Premenstrual dysphoric disorder 4=Other (please specify) 5=Don’t know</t>
+          <t>1=Major depressive disorder 2=Dysthymia or persistent depressive disorder 3=Premenstrual dysphoric disorder 4=Others  5=Don’t know</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -3335,7 +3335,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1=Bipolar I disorder 2=Bipolar II disorder 3=Cyclothymic disorder 4=Other (please specify) 5=Don’t know</t>
+          <t>1=Bipolar I disorder 2=Bipolar II disorder 3=Cyclothymic disorder 4=Others  5=Don’t know</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3389,7 +3389,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1 =Generalized anxiety disorder 2=Panic disorder 3=Agoraphobia 4=Specific phobia (e.g., claustrophobia, arachnophobia, etc.) 5=Social anxiety disorder (or social phobia) 6=Other (please specify) 7=Don’t know</t>
+          <t>1 =Generalized anxiety disorder 2=Panic disorder 3=Agoraphobia 4=Specific phobia (e.g., claustrophobia, arachnophobia, etc.) 5=Social anxiety disorder (or social phobia) 6=Others  7=Don’t know</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3443,7 +3443,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1=Obsessive-compulsive disorder 2=Body dysmorphic disorder 3=Hoarding disorder 4=Trichotillomania (hair-pulling disorder) 5=Excoriation (skin-picking) disorder 6=Other (please specify) 7=Don’t know</t>
+          <t>1=Obsessive-compulsive disorder 2=Body dysmorphic disorder 3=Hoarding disorder 4=Trichotillomania (hair-pulling disorder) 5=Excoriation (skin-picking) disorder 6=Others 7=Don’t know</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3497,7 +3497,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1=Post-traumatic stress disorder 2=Acute stress disorder 3=Adjustment disorder 4=Other (please specify) 5=Don’t know</t>
+          <t>1=Post-traumatic stress disorder 2=Acute stress disorder 3=Adjustment disorder 4=Others  5=Don’t know</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3551,7 +3551,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1=Attention deficit hyperactivity disorder (ADHD or ADD) 2=Other intellectual disability 3=Autism spectrum disorder 4=Other (please specify) 5=Don’t know</t>
+          <t>1=Attention deficit hyperactivity disorder (ADHD or ADD) 2=Other intellectual disability 3=Autism spectrum disorder 4=Others  5=Don’t know</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3605,7 +3605,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1=Anorexia nervosa 2=Bulimia nervosa 3=Binge-eating disorder 4=Pica 5=Avoidant/restrictive food intake disorder (selective eating disorder) 6=Other (please specify) 7=Don’t know</t>
+          <t>1=Anorexia nervosa 2=Bulimia nervosa 3=Binge-eating disorder 4=Pica 5=Avoidant/restrictive food intake disorder (selective eating disorder) 6=Others 7=Don’t know</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1=Schizophrenia 2=Schizo-affective disorder 3=Brief psychotic disorder 4=Delusional disorder 5=Schizophreniform disorder 6=Other (please specify) 7=Don’t know</t>
+          <t>1=Schizophrenia 2=Schizo-affective disorder 3=Brief psychotic disorder 4=Delusional disorder 5=Schizophreniform disorder 6=Others  7=Don’t know</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3713,7 +3713,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1=Antisocial personality disorder 2=Avoidant personality disorder 3=Borderline personality disorder 4=Dependent personality disorder 5=Histrionic personality disorder 6=Narcissistic personality disorder 7=Obsessive-Compulsive personality disorder 8=Paranoid personality disorder 9=Schizoid personality disorder 10=Schizotypal personality disorder 11=Other (please specify) 12=Don’t know</t>
+          <t>1=Antisocial personality disorder 2=Avoidant personality disorder 3=Borderline personality disorder 4=Dependent personality disorder 5=Histrionic personality disorder 6=Narcissistic personality disorder 7=Obsessive-Compulsive personality disorder 8=Paranoid personality disorder 9=Schizoid personality disorder 10=Schizotypal personality disorder 11=Others 12=Don’t know</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1=Alcohol abuse or other alcohol-related disorders 4=Opioid Use Disorder 2=Other (please specify) 3=Don’t know</t>
+          <t>1=Alcohol abuse or other alcohol-related disorders 4=Opioid Use Disorder 2=Others  3=Don’t know</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -3817,7 +3817,7 @@
       <c r="E13" s="2" t="inlineStr"/>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>1=Attention deficit/hyperactivity disorders 2=Deaf or hard of hearing 3=Learning disorders 4=Mobility Impairments 5=Neurological disorders 6=Physical/health related disorders 7=Psychological disorder/condition 8=Visual impairments 9=Other (please specify) 10=Prefer not to respond [mutually exclusive] 11=I do not have a disability[mutually exclusive]</t>
+          <t>1=Attention deficit/hyperactivity disorders 2=Deaf or hard of hearing 3=Learning disorders 4=Mobility Impairments 5=Neurological disorders 6=Physical/health related disorders 7=Psychological disorder/condition 8=Visual impairments 9=Others 10=Prefer not to respond [mutually exclusive] 11=I do not have a disability[mutually exclusive]</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>0=No treatment 1=Medication only 2=Therapy only (e.g., CBT for ADHD, Executive Function Coaching, etc.) 3=Medication and therapy 4=Other (please specify)</t>
+          <t>0=No treatment 1=Medication only 2=Therapy only (e.g., CBT for ADHD, Executive Function Coaching, etc.) 3=Medication and therapy 4=Others</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4055,7 +4055,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>0=No treatment 1=Medication only 2=Therapy only (e.g., CBT for ADHD, Executive Function Coaching, etc.) 3=Medication and therapy 4=Other (please specify)</t>
+          <t>0=No treatment 1=Medication only 2=Therapy only (e.g., CBT for ADHD, Executive Function Coaching, etc.) 3=Medication and therapy 4=Others</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4391,7 +4391,7 @@
       <c r="E22" s="2" t="inlineStr"/>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1=Professional clinician (e.g., psychologist, counselor, or psychiatrist) 2=Roommate 3=Friend (who is not a roommate) 4=Significant other/romantic partner 5=Family member 6=Religious counselor or other religious contact 7=Support group 8=Other non-clinical source (please specify) 9=No one [mutually exclusive]</t>
+          <t>1=Professional clinician (e.g., psychologist, counselor, or psychiatrist) 2=Roommate 3=Friend (who is not a roommate) 4=Significant other/romantic partner 5=Family member 6=Religious counselor or other religious contact 7=Support group 8=Other non-clinical source 9=No one [mutually exclusive]</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -4400,7 +4400,7 @@
         </is>
       </c>
       <c r="H22" s="2" t="n">
-        <v>28.36</v>
+        <v>29.91</v>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
@@ -4431,7 +4431,7 @@
         </is>
       </c>
       <c r="O22" s="2" t="n">
-        <v>0.393</v>
+        <v>0.39</v>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
@@ -4651,7 +4651,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1=YourDost 2=Psychiatric Emergency Services/Psych Emergency Room (ER) 3=Inpatient psychiatric hospital 4=Partial hospitalization program 5=Provider in the local community (not on campus) 6=Provider in another location (such as your hometown) 7=Other</t>
+          <t>1=YourDost 2=Psychiatric Emergency Services/Psych Emergency Room (ER) 3=Inpatient psychiatric hospital 4=Partial hospitalization program 5=Provider in the local community (not on campus) 6=Provider in another location (such as your hometown) 7=Others</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -4690,7 +4690,7 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted? [pipe in selected options from the question, “From which of the following places did you receive counseling or therapy?”]</t>
+          <t xml:space="preserve">Of the places you reported receiving counseling or therapy, how were your counseling or therapy sessions conducted? </t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
@@ -4971,7 +4971,7 @@
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health (please specify) 8=No, none of these [mutually exclusive] 9=Don’t know</t>
+          <t>1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don’t know</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -5047,7 +5047,7 @@
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>1=Mental or emotional health 2=Other health reasons 3=Academic performance 4=Recreation/fun 5=Other (please specify)</t>
+          <t>1=Mental or emotional health 2=Other health reasons 3=Academic performance 4=Recreation/fun 5=Others</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="F34" s="2" t="inlineStr">
         <is>
-          <t>1=Mental or emotional health 2=Other health reasons 3=Academic performance 4=Recreation/fun 5=Other (please specify)</t>
+          <t>1=Mental or emotional health 2=Other health reasons 3=Academic performance 4=Recreation/fun 5=Others</t>
         </is>
       </c>
       <c r="G34" s="2" t="inlineStr">
@@ -5209,7 +5209,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1=A general practitioner, nurse practitioner, or primary care physician 2=A psychiatrist 3=Other type of doctor (please specify) 4=Took the medication(s) without a prescription 5=Don’t know</t>
+          <t>1=A general practitioner, nurse practitioner, or primary care physician 2=A psychiatrist 3=Other type of doctor  4=Took the medication(s) without a prescription 5=Don’t know</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -5263,7 +5263,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1=Psychostimulants (methylphenidate (Ritalin, or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health (please specify) 8=None of the above [mutually exclusive]</t>
+          <t>1=Psychostimulants (methylphenidate (Ritalin, or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health  8=None of the above [mutually exclusive]</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -5425,7 +5425,7 @@
       </c>
       <c r="F40" s="2" t="inlineStr">
         <is>
-          <t>1=YourDost 2=Urgent Care or the Emergency Room 3=Provider in the local community (not on campus) 4=Provider in my hometown 5=Provider affiliated with a telehealth company 6=Other (please specify)</t>
+          <t xml:space="preserve">1=YourDost 2=Urgent Care or the Emergency Room 3=Provider in the local community (not on campus) 4=Provider in my hometown 5=Provider affiliated with a telehealth company 6=Other </t>
         </is>
       </c>
       <c r="G40" s="2" t="inlineStr">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help (please specify the person's relationship to you). 7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help 8=I acquired more information about my options from (please specify where). 10= A health professional recommended or referred me to seek help. 12=Other (please specify)</t>
+          <t>1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help  7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help 8=I acquired more information about my options from  10= A health professional recommended or referred me to seek help. 12=Others</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">
@@ -5691,7 +5691,7 @@
       <c r="E45" s="2" t="inlineStr"/>
       <c r="F45" s="2" t="inlineStr">
         <is>
-          <t>1=No need for services 2=Financial reasons (too expensive, not covered by insurance) 3=Not enough time 4=Not sure where to go 5=Difficulty finding an available appointment 6=Prefer to deal with issues on my own or with support from family/friends 7=Privacy concerns 8= People providing services don’t understand me 9=Other (please specify) 10= No barriers [mutually exclusive] 11= fear of being mistreated due to my identity/identities 12=The clinic or clinician had limits on the number of times I could be seen</t>
+          <t>1=No need for services 2=Financial reasons (too expensive, not covered by insurance) 3=Not enough time 4=Not sure where to go 5=Difficulty finding an available appointment 6=Prefer to deal with issues on my own or with support from family/friends 7=Privacy concerns 8= People providing services don’t understand me 9=Other 10= No barriers [mutually exclusive] 11= fear of being mistreated due to my identity/identities 12=The clinic or clinician had limits on the number of times I could be seen</t>
         </is>
       </c>
       <c r="G45" s="2" t="inlineStr">
@@ -5700,7 +5700,7 @@
         </is>
       </c>
       <c r="H45" s="2" t="n">
-        <v>44.62</v>
+        <v>45.8</v>
       </c>
       <c r="I45" s="2" t="inlineStr">
         <is>
@@ -5731,7 +5731,7 @@
         </is>
       </c>
       <c r="O45" s="2" t="n">
-        <v>0.594</v>
+        <v>0.592</v>
       </c>
       <c r="P45" s="2" t="inlineStr">
         <is>
@@ -5763,7 +5763,7 @@
       <c r="E46" s="2" t="inlineStr"/>
       <c r="F46" s="2" t="inlineStr">
         <is>
-          <t>1=I haven’t had the chance to go but I plan to. 2=No need for services 3=Financial reasons (too expensive, not covered by insurance) 4=Not enough time 5=Not sure where to go 6=Difficulty finding an available appointment 7=Prefer to deal with issues on my own or with support from family/friends 8=Other (please specify) 9=No barriers [mutually exclusive] 10=Privacy concerns 11=People providing services don’t understand me 12=Fear of being mistreated due to my identity/identities 13=The clinic or clinician had limits on the number of times I could be seen</t>
+          <t>1=I haven’t had the chance to go but I plan to. 2=No need for services 3=Financial reasons (too expensive, not covered by insurance) 4=Not enough time 5=Not sure where to go 6=Difficulty finding an available appointment 7=Prefer to deal with issues on my own or with support from family/friends 8=Others  9=No barriers [mutually exclusive] 10=Privacy concerns 11=People providing services don’t understand me 12=Fear of being mistreated due to my identity/identities 13=The clinic or clinician had limits on the number of times I could be seen</t>
         </is>
       </c>
       <c r="G46" s="2" t="inlineStr">
@@ -5772,7 +5772,7 @@
         </is>
       </c>
       <c r="H46" s="2" t="n">
-        <v>53.89</v>
+        <v>55.18</v>
       </c>
       <c r="I46" s="2" t="inlineStr">
         <is>
@@ -5803,7 +5803,7 @@
         </is>
       </c>
       <c r="O46" s="2" t="n">
-        <v>0.576</v>
+        <v>0.573</v>
       </c>
       <c r="P46" s="2" t="inlineStr">
         <is>
@@ -5835,7 +5835,7 @@
       <c r="E47" s="2" t="inlineStr"/>
       <c r="F47" s="2" t="inlineStr">
         <is>
-          <t>1=Roommate 2=Friend (who is not a roommate) 3=Significant other 4=Family member 5=Religious counselor or other religious contact 6=Support group 9=Faculty member/professor/instructor 10=Staff member 7=Other non-clinical source (please specify) 8=No, none of these [mutually exclusive]</t>
+          <t>1=Roommate 2=Friend (who is not a roommate) 3=Significant other 4=Family member 5=Religious counselor or other religious contact 6=Support group 9=Faculty member/professor/instructor 10=Staff member 7=Other non-clinical source  8=No, none of these [mutually exclusive]</t>
         </is>
       </c>
       <c r="G47" s="2" t="inlineStr">
@@ -5844,7 +5844,7 @@
         </is>
       </c>
       <c r="H47" s="2" t="n">
-        <v>40.1</v>
+        <v>41.97</v>
       </c>
       <c r="I47" s="2" t="inlineStr">
         <is>
@@ -5875,7 +5875,7 @@
         </is>
       </c>
       <c r="O47" s="2" t="n">
-        <v>0.52</v>
+        <v>0.516</v>
       </c>
       <c r="P47" s="2" t="inlineStr">
         <is>
@@ -5961,7 +5961,7 @@
       <c r="E49" s="2" t="inlineStr"/>
       <c r="F49" s="2" t="inlineStr">
         <is>
-          <t>1=Professor/Instructor from one of my classes 2=Academic advisor/academic counselor 3=Another faculty member or instructor 4=Teaching assistant 5=Student services staff 6=Dean of Students or class dean 7=Other (please specify) 8=No one [mutually exclusive]</t>
+          <t>1=Professor/Instructor from one of my classes 2=Academic advisor/academic counselor 3=Another faculty member or instructor 4=Teaching assistant 5=Student services staff 6=Dean of Students or class dean 7=Others  8=No one [mutually exclusive]</t>
         </is>
       </c>
       <c r="G49" s="2" t="inlineStr">
@@ -5970,7 +5970,7 @@
         </is>
       </c>
       <c r="H49" s="2" t="n">
-        <v>40.19</v>
+        <v>42.15</v>
       </c>
       <c r="I49" s="2" t="inlineStr">
         <is>
@@ -6001,11 +6001,11 @@
         </is>
       </c>
       <c r="O49" s="2" t="n">
-        <v>0.603</v>
+        <v>0.599</v>
       </c>
       <c r="P49" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="Q49" s="2" t="inlineStr">
@@ -6355,7 +6355,7 @@
       </c>
       <c r="F55" s="2" t="inlineStr">
         <is>
-          <t>1=…doesn’t cover any mental health services. 2=…doesn’t cover pre existing conditions. 3=…doesn’t cover certain conditions. 4=…has a co-pay that is too expensive. 5=…has a deductible that is too expensive. 6=…doesn’t cover certain types of services or providers. 7=…has a limit on the number of services that are covered. 8=Other (please specify)</t>
+          <t>1=…doesn’t cover any mental health services. 2=…doesn’t cover pre existing conditions. 3=…doesn’t cover certain conditions. 4=…has a co-pay that is too expensive. 5=…has a deductible that is too expensive. 6=…doesn’t cover certain types of services or providers. 7=…has a limit on the number of services that are covered. 8=Others</t>
         </is>
       </c>
       <c r="G55" s="2" t="inlineStr">
@@ -6603,7 +6603,7 @@
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1=Diabetes 2=High blood pressure 3=Asthma 4=Thyroid disease (e.g., hypothyroid or hyperthyroid) 5=Gastrointestinal disease (e.g., Crohn’s Disease, Ulcerative Colitis) 6=Arthritis 7=Sickle cell anemia 8=Seizure disorders (e.g., epilepsy) 9=Cancers 10=High cholesterol 11=HIV/AIDS 12=Other autoimmune disorder (please specify) 13=Other chronic disease (please specify) 14=No, never been diagnosed with a chronic disease. [mutually exclusive] 15=Don’t know [mutually exclusive]</t>
+          <t>1=Diabetes 2=High blood pressure 3=Asthma 4=Thyroid disease (e.g., hypothyroid or hyperthyroid) 5=Gastrointestinal disease (e.g., Crohn’s Disease, Ulcerative Colitis) 6=Arthritis 7=Sickle cell anemia 8=Seizure disorders (e.g., epilepsy) 9=Cancers 10=High cholesterol 11=HIV/AIDS 12=Other autoimmune disorder  13=Other chronic disease  14=No, never been diagnosed with a chronic disease. [mutually exclusive] 15=Don’t know [mutually exclusive]</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -6612,7 +6612,7 @@
         </is>
       </c>
       <c r="H3" s="2" t="n">
-        <v>23.49</v>
+        <v>25.16</v>
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
@@ -6643,7 +6643,7 @@
         </is>
       </c>
       <c r="O3" s="2" t="n">
-        <v>0.32</v>
+        <v>0.316</v>
       </c>
       <c r="P3" s="2" t="inlineStr">
         <is>
@@ -6823,7 +6823,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1=I exercise more now. 2=I exercise less now. 3=Other (please specify)</t>
+          <t>1=I exercise more now. 2=I exercise less now. 3=Others</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6920,11 +6920,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="Q7" s="2" t="inlineStr">
-        <is>
-          <t>help to remember times you went to the hospital or</t>
-        </is>
-      </c>
+      <c r="Q7" s="2" t="inlineStr"/>
       <c r="R7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
@@ -6996,11 +6992,7 @@
           <t>Low</t>
         </is>
       </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>help to remember times you went to the hospital or</t>
-        </is>
-      </c>
+      <c r="Q8" s="2" t="inlineStr"/>
       <c r="R8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
@@ -7351,7 +7343,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>1= To improve my overall health. 2= To manage a specific health condition. 3= To lose weight. 4= To spend less money on food. 5= To reduce my carbon footprint or protect the environment. 6=Other (text)</t>
+          <t>1= To improve my overall health. 2= To manage a specific health condition. 3= To lose weight. 4= To spend less money on food. 5= To reduce my carbon footprint or protect the environment. 6=Others</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7405,7 +7397,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>1= To improve my overall health. 2= To manage a specific health condition. 3= To lose weight. 4= To spend less money on food. 5= To reduce my carbon footprint or protect the environment. 6=Other</t>
+          <t>1= To improve my overall health. 2= To manage a specific health condition. 3= To lose weight. 4= To spend less money on food. 5= To reduce my carbon footprint or protect the environment. 6=Others</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8182,7 +8174,7 @@
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1=Financial challenges 2=Mental or emotional health problems 3=Other health problems (not directly related to mental or emotional health) 4=Family obligations 5=Family or relationship difficulties 6=Academic challenges (struggling to pass classes) 7=[if not U.S. citizen, ask→Visa or other challenges related to being a non-U.S. citizen] 8=Lack of motivation or desire 9=Work or professional commitments 10=Career opportunities 11=Other challenge(s) (please specify)</t>
+          <t>1=Financial challenges 2=Mental or emotional health problems 3=Other health problems (not directly related to mental or emotional health) 4=Family obligations 5=Family or relationship difficulties 6=Academic challenges (struggling to pass classes) 7=Lack of motivation or desire 8=Work or professional commitments 9=Career opportunities 10=Others</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8191,7 +8183,7 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>32.37</v>
+        <v>22.3</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
@@ -8222,7 +8214,7 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.219</v>
+        <v>0.239</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
@@ -8254,7 +8246,7 @@
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1=2-year college degree (associate’s) 2=4-year college degree (bachelor’s) 3=Master’s degree 4=Doctoral degree (JD, MD, Ph D, etc.) 5=Other degree (please specify) 6=Don’t know</t>
+          <t>1=2-year college degree (associate’s) 2=4-year college degree (bachelor’s) 3=Master’s degree 4=Doctoral degree (JD, MD, Ph D, etc.) 5=Other degree  6=Don’t know</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8263,7 +8255,7 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>63.98</v>
+        <v>68.31999999999999</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -8294,7 +8286,7 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.07199999999999999</v>
+        <v>0.063</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
@@ -8774,7 +8766,7 @@
       <c r="E16" s="2" t="inlineStr"/>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1=I did not experience this. 2=I experienced this but it did not affect my academic performance. 3=I received a lower grade on one or more exams or projects. 4=I received a lower grade in one or more courses. 5=I received an incomplete or dropped one or more courses. 6=I had a significant disruption in research, practicum, thesis, or dissertation work. 7=Other (please specify)</t>
+          <t>1=I did not experience this. 2=I experienced this but it did not affect my academic performance. 3=I received a lower grade on one or more exams or projects. 4=I received a lower grade in one or more courses. 5=I received an incomplete or dropped one or more courses. 6=I had a significant disruption in research, practicum, thesis, or dissertation work. 7=Others</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8783,7 +8775,7 @@
         </is>
       </c>
       <c r="H16" s="2" t="n">
-        <v>18.68</v>
+        <v>19.51</v>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
@@ -8814,7 +8806,7 @@
         </is>
       </c>
       <c r="O16" s="2" t="n">
-        <v>0.696</v>
+        <v>0.694</v>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
@@ -9405,7 +9397,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>What are those concerns? (Select all that apply.</t>
+          <t>What are those concerns? (Select all that apply)</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -9420,7 +9412,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1=Condition/quality of housing 2=Lack of more permanent housing 3=Ability to pay for housing or utilities 4=Feeling safe 5=Other (please specify)</t>
+          <t>1=Condition/quality of housing 2=Lack of more permanent housing 3=Ability to pay for housing or utilities 4=Feeling safe 5=Others</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -9470,7 +9462,7 @@
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1=Family resources (parents, relatives, spouse, etc.) 2=Your own resources (income from work, work-study, etc.) 3=Aid that need not be repaid (grants, scholarships, military, etc.) 4=Aid that must be repaid (loans) 5=Other sources (please specify)</t>
+          <t>1=Family resources (parents, relatives, spouse, etc.) 2=Your own resources (income from work, work-study, etc.) 3=Aid that need not be repaid (grants, scholarships, military, etc.) 4=Aid that must be repaid (loans) 5=Other sources</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -9479,7 +9471,7 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>57</v>
+        <v>59.75</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -9510,7 +9502,7 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.169</v>
+        <v>0.164</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
@@ -9614,7 +9606,7 @@
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1=No [mutually exclusive] 2=Yes, a need based scholarship 3=Yes, an academic scholarship (or merit scholarship) 4=Yes, an athletic scholarship 5=Other (please specify)</t>
+          <t>1=No [mutually exclusive] 2=Yes, a need based scholarship 3=Yes, an academic scholarship (or merit scholarship) 4=Yes, an athletic scholarship 5=Others</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9623,7 +9615,7 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>31.88</v>
+        <v>34.87</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -9654,7 +9646,7 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>0.22</v>
+        <v>0.214</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
@@ -9751,7 +9743,7 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>How often have you used online sportsbook applications (e.g., Draftkings, Fanduel, Bet MGM) in the past year in order to participate in sports betting?</t>
+          <t>How often have you used online sportsbook applications (e.g., Dream11,Parimatch,Dafabet) in the past year in order to participate in sports betting?</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -22,16 +22,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b val="1"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -63,7 +60,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -71,24 +68,18 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -5273,12 +5273,12 @@
       <c r="P37" s="2" t="inlineStr"/>
       <c r="Q37" s="2" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
       <c r="R37" s="2" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
     </row>
@@ -5543,12 +5543,12 @@
       <c r="P42" s="2" t="inlineStr"/>
       <c r="Q42" s="2" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
       <c r="R42" s="2" t="inlineStr">
         <is>
-          <t>Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
+          <t>Display if "8=No, none of these" is not selected for "In the past 12 months have you taken any of the following types of prescription medications?" Pipe in selected options from: “In the past 12 months have you taken any of the following types of prescription medications?”</t>
         </is>
       </c>
     </row>

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -6158,7 +6158,7 @@
       <c r="E52" s="2" t="inlineStr"/>
       <c r="F52" s="2" t="inlineStr">
         <is>
-          <t>1=I do not have any health insurance coverage (uncovered). [mutually exclusive] 2=I have health insurance through my parent/guardian(s) or their employer. 3=I have health insurance through my employer. 4=I have health insurance through my spouse’s employer. 5=I have a student health insurance plan. 6=I have health insurance through an embassy or sponsoring agency for international students. 7=I have individual health insurance purchased directly from an insurance carrier. 8=I have Medicaid or other governmental insurance. 9=I am uncertain about whether I have health insurance. 10=I have health insurance but am uncertain about where it is from.</t>
+          <t>1=I do not have any health insurance coverage (uncovered). [mutually exclusive] 2=I have health insurance through my parent/guardian(s) or their employer. 3=I have health insurance through my employer. 4=I have health insurance through my spouse’s employer. 5=I have a student health insurance plan. 6=I have individual health insurance purchased directly from an insurance carrier. 7=I have a governmental insurance plan. 8=I am uncertain about whether I have health insurance.[mutually exclusive] 9=I have health insurance but am uncertain about where it is from.[mutually exclusive]</t>
         </is>
       </c>
       <c r="G52" s="2" t="inlineStr">
@@ -6167,7 +6167,7 @@
         </is>
       </c>
       <c r="H52" s="2" t="n">
-        <v>33.45</v>
+        <v>33.82</v>
       </c>
       <c r="I52" s="2" t="inlineStr">
         <is>

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -5617,7 +5617,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Which of the following are important reasons why you received those services? (Select all that apply)</t>
+          <t>Which of the following are important reasons why you received the counselling services? (Select all that apply)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -8943,7 +8943,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -9019,7 +9019,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -9095,7 +9095,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -9239,7 +9239,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Socioeconom ic status</t>
+          <t>Socioeconomic status</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -8654,12 +8654,12 @@
       </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
-          <t>Display if selected “6=PhD (or equivalent doctoral program” as degree program.</t>
+          <t>Display if "MS by Research scholar" or "PhD Scholar" is selected for "What is your role at IIITB?" (Faculty Advising is a PhD/research-degree program dependency -- references the Demographics Role question, not a question in this module.</t>
         </is>
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>Display if selected “6=PhD (or equivalent doctoral program” as degree program.</t>
+          <t>Display if "MS by Research scholar" or "PhD Scholar" is selected for "What is your role at IIITB?" (Faculty Advising is a PhD/research-degree program dependency -- references the Demographics Role question, not a question in this module.</t>
         </is>
       </c>
     </row>

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -1718,7 +1718,7 @@
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0=No 1=Yes</t>
+          <t>1=Yes 0=No</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4962,7 +4962,7 @@
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1=Psychostimulants (methylphenidate (Ritalin or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don’t know</t>
+          <t>1=Psychostimulants (methylphenidate, amphetamine salts), dextroamphetamine, etc.) 2=Antidepressants (e.g., fluoxetin,sertraline,paroxetine,escitalopra,venlafaxine,bupropion, etc.) 3=Antipsychotics (e.g., haloperidol,clozapine,risperidone,olanzapine,etc.) 4=Anti-anxiety medications (e.g., lorazepam,clonazepam,alprazolam,buspirone,etc.) 5=Mood stabilizers (e.g., lithium, valproate,lamotrigine,carbamazepine,etc.) 6=Sleep medications (e.g., zolpidem,zaleplon,etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don’t know</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4971,7 +4971,7 @@
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>0</v>
+        <v>1.39</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
@@ -5002,11 +5002,11 @@
         </is>
       </c>
       <c r="O32" s="2" t="n">
-        <v>0.6</v>
+        <v>0.597</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
@@ -5254,7 +5254,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1=Psychostimulants (methylphenidate (Ritalin, or Concerta), amphetamine salts (Adderall), dextroamphetamine (Dexedrine), etc.) 2=Antidepressants (e.g., fluoxetine (Prozac), sertraline (Zoloft), paroxetine (Paxil), escitalopram (Lexapro), venlafaxine (Effexor), bupropion (Wellbutrin), etc.) 3=Antipsychotics (e.g., haloperidol (Haldol), clozapine (Clozaril), risperidone (Risperdal), olanzapine (Zyprexas), etc.) 4=Anti-anxiety medications (e.g., lorazepam (Ativan), clonazepam (Klonopin), alprazolam (Xanax), buspirone (Bu Spar), etc.) 5=Mood stabilizers (e.g., lithium, valproate (Depakote), lamotrigine (Lamictal), carbamazepine (Tegretol), etc.) 6=Sleep medications (e.g., zolpidem (Ambien), zaleplon (Sonata), etc.) 7=Other medication for mental or emotional health  8=None of the above [mutually exclusive]</t>
+          <t>1=Psychostimulants (methylphenidate, amphetamine salts), dextroamphetamine, etc.) 2=Antidepressants (e.g., fluoxetin,sertraline,paroxetine,escitalopra,venlafaxine,bupropion, etc.) 3=Antipsychotics (e.g., haloperidol,clozapine,risperidone,olanzapine,etc.) 4=Anti-anxiety medications (e.g., lorazepam,clonazepam,alprazolam,buspirone,etc.) 5=Mood stabilizers (e.g., lithium, valproate,lamotrigine,carbamazepine,etc.) 6=Sleep medications (e.g., zolpidem,zaleplon,etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don’t know</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>How frequently do instructors in your major/field of study grade your work on a curve (adjust grades based on the grade distribution among students in a class)?</t>
+          <t xml:space="preserve">How often do professors or external examiners in your course/department use relative grading (scaling or adjusting marks based on the overall performance of the class rather than using fixed passing marks)? </t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
@@ -7873,11 +7873,11 @@
         </is>
       </c>
       <c r="H4" s="2" t="n">
-        <v>40.11</v>
+        <v>22.47</v>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7891,7 +7891,7 @@
         </is>
       </c>
       <c r="L4" s="2" t="n">
-        <v>0.299</v>
+        <v>0.388</v>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
@@ -7900,11 +7900,11 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>Reading</t>
+          <t>Clarity, Reading</t>
         </is>
       </c>
       <c r="O4" s="2" t="n">
-        <v>0.253</v>
+        <v>0.372</v>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
@@ -8370,7 +8370,7 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>How has it been to adjust to the academic demands of [college/graduate school] since you began as a student at your school?</t>
+          <t>How has it been to adjust to the academic demands of college since you began as a student at your school?</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
@@ -8390,7 +8390,7 @@
         </is>
       </c>
       <c r="H11" s="2" t="n">
-        <v>48.23</v>
+        <v>49.51</v>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
@@ -8421,7 +8421,7 @@
         </is>
       </c>
       <c r="O11" s="2" t="n">
-        <v>0.27</v>
+        <v>0.268</v>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
@@ -8690,7 +8690,7 @@
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>Likert (6-point)</t>
+          <t>Matrix</t>
         </is>
       </c>
       <c r="H15" s="2" t="n">
@@ -8708,11 +8708,11 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L15" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
@@ -8725,14 +8725,18 @@
         </is>
       </c>
       <c r="O15" s="2" t="n">
-        <v>0.357</v>
+        <v>0.407</v>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q15" s="2" t="inlineStr"/>
+      <c r="Q15" s="2" t="inlineStr">
+        <is>
+          <t>Matrix table with 2 questions.</t>
+        </is>
+      </c>
       <c r="R15" s="2" t="inlineStr"/>
     </row>
     <row r="16">

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -9441,7 +9441,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Housing concerns</t>
+          <t>Financing education</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -1718,7 +1718,7 @@
       <c r="E11" s="2" t="inlineStr"/>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1=Yes 0=No</t>
+          <t>0=No 1=Yes</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9534,7 +9534,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Likert (6-point)</t>
+          <t>Matrix</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
@@ -9552,11 +9552,11 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -9569,14 +9569,18 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.597</v>
+        <v>0.647</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr"/>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Matrix table with 3 statements.</t>
+        </is>
+      </c>
       <c r="R10" s="2" t="inlineStr"/>
     </row>
     <row r="11">

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -8314,7 +8314,7 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Likert (6-point)</t>
+          <t>Matrix</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
@@ -8332,11 +8332,11 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -8349,14 +8349,18 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.374</v>
+        <v>0.424</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
           <t>Medium</t>
         </is>
       </c>
-      <c r="Q10" s="2" t="inlineStr"/>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>Matrix table with 3 statements.</t>
+        </is>
+      </c>
       <c r="R10" s="2" t="inlineStr"/>
     </row>
     <row r="11">

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -1627,7 +1627,7 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Please answer the following questions as honestly as possible. Do you often feel the desire to eat when you are emotionally upset or stressed? Do you often feel that you can't control what or how much you eat? Do you sometimes make yourself throw up (vomit) to control your weight? Are you often preoccupied with a desire to be thinner? Do you believe yourself to be fat when others say you are thin?</t>
+          <t>Please answer the following questions as honestly as possible. 1. Do you often feel the desire to eat when you are emotionally upset or stressed? 2. Do you often feel that you can't control what or how much you eat? 3. Do you sometimes make yourself throw up (vomit) to control your weight? 4. Are you often preoccupied with a desire to be thinner? 5. Do you believe yourself to be fat when others say you are thin?</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -1643,15 +1643,15 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>Boolean</t>
+          <t>Matrix</t>
         </is>
       </c>
       <c r="H10" s="2" t="n">
-        <v>68.06999999999999</v>
+        <v>74.13</v>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>Moderate</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1661,11 +1661,11 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="L10" s="2" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
@@ -1678,7 +1678,7 @@
         </is>
       </c>
       <c r="O10" s="2" t="n">
-        <v>0.397</v>
+        <v>0.435</v>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
@@ -1687,14 +1687,10 @@
       </c>
       <c r="Q10" s="2" t="inlineStr">
         <is>
-          <t>Included if ‘Eating and Body Image’ module not selected SDE (Maguen et al., 2018)</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>Included if ‘Eating and Body Image’ module not selected SDE (Maguen et al., 2018)</t>
-        </is>
-      </c>
+          <t xml:space="preserve">Matrix </t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n">
@@ -2170,7 +2166,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>1=0 times 2=1 time 3=2 times 4=3 to 5 times 5=6 to 9 times 6=10 or more times 7=Don’t know</t>
+          <t xml:space="preserve">1=0 times 2=1 time 3=2 times 4=3 to 5 times 5=6 to 9 times 6=10 or more times 7=Don't know [mutually exclusive] </t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2778,7 +2774,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1=An official institutional communication (e.g., email, emergency alert system) 2=A memorial 3=News media (e.g., newspapers or blogs) 4=Social media (e.g., Reddit, Instagram, Meta, X) 5=Word of mouth from my peers 6=Others  7=I don’t remember 8=None of these</t>
+          <t>1=An official institutional communication (e.g., email, emergency alert system) 2=A memorial 3=News media (e.g., newspapers or blogs) 4=Social media (e.g., Reddit, Instagram, Meta, X) 5=Word of mouth from my peers 6=Others  7=I don’t remember [mutually exclusive] 8=None of these</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3020,7 +3016,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>1=No negative experience 2=Harassed/Bullied online 3=Cyber stalking 4=Flaming, whereby someone is being encouraged (egged on) to die by suicide 5=Had someone create/share embarrassing images of you using Ai (e.g., deep fakes) 6=Imposter Scam,for falsely demanding money from family and friends 7=Others</t>
+          <t>1=No negative experience [mutually exclusive] 2=Harassed/Bullied online 3=Cyber stalking 4=Flaming, whereby someone is being encouraged (egged on) to die by suicide 5=Had someone create/share embarrassing images of you using Ai (e.g., deep fakes) 6=Imposter Scam,for falsely demanding money from family and friends 7=Others</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3196,7 +3192,7 @@
       <c r="E2" s="2" t="inlineStr"/>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>1=Depression (e.g., major depressive disorder, persistent depressive disorder) 2=Bipolar (e.g., bipolar I or II, cyclothymia) 3=Anxiety (e.g., generalized anxiety disorder, phobias) 4=Obsessive-compulsive or related disorders (e.g., obsessive-compulsive disorder, body dysmorphia) 5=Trauma and Stressor Related Disorders (e.g, post-traumatic stress disorder), 6=Neurodevelopmental disorder or intellectual disability (e.g., attention deficit disorder (ADD), attention deficit hyperactivity disorder (ADHD), intellectual disability, autism spectrum disorder) 7=Eating disorder (e.g., anorexia nervosa, bulimia nervosa) 8=Psychosis (e.g., schizophrenia, schizo-affective disorder) 9=Personality disorder (e.g., antisocial personality disorder, paranoid personality disorder, schizoid personality disorder) 10=Substance use disorder (e.g., alcohol abuse, abuse of other drugs) 11=No, none of these [mutually exclusive] 12=Don’t know 13=Other mental health condition (please specify)</t>
+          <t>1=Depression (e.g., major depressive disorder, persistent depressive disorder) 2=Bipolar (e.g., bipolar I or II, cyclothymia) 3=Anxiety (e.g., generalized anxiety disorder, phobias) 4=Obsessive-compulsive or related disorders (e.g., obsessive-compulsive disorder, body dysmorphia) 5=Trauma and Stressor Related Disorders (e.g, post-traumatic stress disorder), 6=Neurodevelopmental disorder or intellectual disability (e.g., attention deficit disorder (ADD), attention deficit hyperactivity disorder (ADHD), intellectual disability, autism spectrum disorder) 7=Eating disorder (e.g., anorexia nervosa, bulimia nervosa) 8=Psychosis (e.g., schizophrenia, schizo-affective disorder) 9=Personality disorder (e.g., antisocial personality disorder, paranoid personality disorder, schizoid personality disorder) 10=Substance use disorder (e.g., alcohol abuse, abuse of other drugs) 11=No, none of these [mutually exclusive] 12=Don't know [mutually exclusive] 13=Other mental health condition (please specify)</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -3272,7 +3268,7 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1=Major depressive disorder 2=Dysthymia or persistent depressive disorder 3=Premenstrual dysphoric disorder 4=Others  5=Don’t know</t>
+          <t>1=Major depressive disorder 2=Dysthymia or persistent depressive disorder 3=Premenstrual dysphoric disorder 4=Others  5=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -3326,7 +3322,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>1=Bipolar I disorder 2=Bipolar II disorder 3=Cyclothymic disorder 4=Others  5=Don’t know</t>
+          <t>1=Bipolar I disorder 2=Bipolar II disorder 3=Cyclothymic disorder 4=Others  5=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3380,7 +3376,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1 =Generalized anxiety disorder 2=Panic disorder 3=Agoraphobia 4=Specific phobia (e.g., claustrophobia, arachnophobia, etc.) 5=Social anxiety disorder (or social phobia) 6=Others  7=Don’t know</t>
+          <t>1 =Generalized anxiety disorder 2=Panic disorder 3=Agoraphobia 4=Specific phobia (e.g., claustrophobia, arachnophobia, etc.) 5=Social anxiety disorder (or social phobia) 6=Others  7=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3434,7 +3430,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>1=Obsessive-compulsive disorder 2=Body dysmorphic disorder 3=Hoarding disorder 4=Trichotillomania (hair-pulling disorder) 5=Excoriation (skin-picking) disorder 6=Others 7=Don’t know</t>
+          <t>1=Obsessive-compulsive disorder 2=Body dysmorphic disorder 3=Hoarding disorder 4=Trichotillomania (hair-pulling disorder) 5=Excoriation (skin-picking) disorder 6=Others 7=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3488,7 +3484,7 @@
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>1=Post-traumatic stress disorder 2=Acute stress disorder 3=Adjustment disorder 4=Others  5=Don’t know</t>
+          <t>1=Post-traumatic stress disorder 2=Acute stress disorder 3=Adjustment disorder 4=Others  5=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -3542,7 +3538,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1=Attention deficit hyperactivity disorder (ADHD or ADD) 2=Other intellectual disability 3=Autism spectrum disorder 4=Others  5=Don’t know</t>
+          <t>1=Attention deficit hyperactivity disorder (ADHD or ADD) 2=Other intellectual disability 3=Autism spectrum disorder 4=Others  5=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3596,7 +3592,7 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1=Anorexia nervosa 2=Bulimia nervosa 3=Binge-eating disorder 4=Pica 5=Avoidant/restrictive food intake disorder (selective eating disorder) 6=Others 7=Don’t know</t>
+          <t>1=Anorexia nervosa 2=Bulimia nervosa 3=Binge-eating disorder 4=Pica 5=Avoidant/restrictive food intake disorder (selective eating disorder) 6=Others 7=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3650,7 +3646,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1=Schizophrenia 2=Schizo-affective disorder 3=Brief psychotic disorder 4=Delusional disorder 5=Schizophreniform disorder 6=Others  7=Don’t know</t>
+          <t>1=Schizophrenia 2=Schizo-affective disorder 3=Brief psychotic disorder 4=Delusional disorder 5=Schizophreniform disorder 6=Others  7=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3704,7 +3700,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>1=Antisocial personality disorder 2=Avoidant personality disorder 3=Borderline personality disorder 4=Dependent personality disorder 5=Histrionic personality disorder 6=Narcissistic personality disorder 7=Obsessive-Compulsive personality disorder 8=Paranoid personality disorder 9=Schizoid personality disorder 10=Schizotypal personality disorder 11=Others 12=Don’t know</t>
+          <t>1=Antisocial personality disorder 2=Avoidant personality disorder 3=Borderline personality disorder 4=Dependent personality disorder 5=Histrionic personality disorder 6=Narcissistic personality disorder 7=Obsessive-Compulsive personality disorder 8=Paranoid personality disorder 9=Schizoid personality disorder 10=Schizotypal personality disorder 11=Others 12=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3758,7 +3754,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1=Alcohol abuse or other alcohol-related disorders 4=Opioid Use Disorder 2=Others  3=Don’t know</t>
+          <t>1=Alcohol abuse or other alcohol-related disorders 4=Opioid Use Disorder 2=Others  3=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4962,7 +4958,7 @@
       <c r="E32" s="2" t="inlineStr"/>
       <c r="F32" s="2" t="inlineStr">
         <is>
-          <t>1=Psychostimulants (methylphenidate, amphetamine salts), dextroamphetamine, etc.) 2=Antidepressants (e.g., fluoxetin,sertraline,paroxetine,escitalopra,venlafaxine,bupropion, etc.) 3=Antipsychotics (e.g., haloperidol,clozapine,risperidone,olanzapine,etc.) 4=Anti-anxiety medications (e.g., lorazepam,clonazepam,alprazolam,buspirone,etc.) 5=Mood stabilizers (e.g., lithium, valproate,lamotrigine,carbamazepine,etc.) 6=Sleep medications (e.g., zolpidem,zaleplon,etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don’t know</t>
+          <t>1=Psychostimulants (methylphenidate, amphetamine salts), dextroamphetamine, etc.) 2=Antidepressants (e.g., fluoxetin,sertraline,paroxetine,escitalopra,venlafaxine,bupropion, etc.) 3=Antipsychotics (e.g., haloperidol,clozapine,risperidone,olanzapine,etc.) 4=Anti-anxiety medications (e.g., lorazepam,clonazepam,alprazolam,buspirone,etc.) 5=Mood stabilizers (e.g., lithium, valproate,lamotrigine,carbamazepine,etc.) 6=Sleep medications (e.g., zolpidem,zaleplon,etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="G32" s="2" t="inlineStr">
@@ -4971,7 +4967,7 @@
         </is>
       </c>
       <c r="H32" s="2" t="n">
-        <v>1.39</v>
+        <v>0</v>
       </c>
       <c r="I32" s="2" t="inlineStr">
         <is>
@@ -5002,11 +4998,11 @@
         </is>
       </c>
       <c r="O32" s="2" t="n">
-        <v>0.597</v>
+        <v>0.6</v>
       </c>
       <c r="P32" s="2" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="Q32" s="2" t="inlineStr"/>
@@ -5146,7 +5142,7 @@
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>1=Not at all 2=1-2 times 3=3-5 times 4=More than 5 times 5=Don’t know</t>
+          <t>1=Not at all 2=1-2 times 3=3-5 times 4=More than 5 times 5=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
@@ -5200,7 +5196,7 @@
       </c>
       <c r="F36" s="2" t="inlineStr">
         <is>
-          <t>1=A general practitioner, nurse practitioner, or primary care physician 2=A psychiatrist 3=Other type of doctor  4=Took the medication(s) without a prescription 5=Don’t know</t>
+          <t>1=A general practitioner, nurse practitioner, or primary care physician 2=A psychiatrist 3=Other type of doctor  4=Took the medication(s) without a prescription 5=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="G36" s="2" t="inlineStr">
@@ -5254,7 +5250,7 @@
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>1=Psychostimulants (methylphenidate, amphetamine salts), dextroamphetamine, etc.) 2=Antidepressants (e.g., fluoxetin,sertraline,paroxetine,escitalopra,venlafaxine,bupropion, etc.) 3=Antipsychotics (e.g., haloperidol,clozapine,risperidone,olanzapine,etc.) 4=Anti-anxiety medications (e.g., lorazepam,clonazepam,alprazolam,buspirone,etc.) 5=Mood stabilizers (e.g., lithium, valproate,lamotrigine,carbamazepine,etc.) 6=Sleep medications (e.g., zolpidem,zaleplon,etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don’t know</t>
+          <t>1=Psychostimulants (methylphenidate, amphetamine salts), dextroamphetamine, etc.) 2=Antidepressants (e.g., fluoxetin,sertraline,paroxetine,escitalopra,venlafaxine,bupropion, etc.) 3=Antipsychotics (e.g., haloperidol,clozapine,risperidone,olanzapine,etc.) 4=Anti-anxiety medications (e.g., lorazepam,clonazepam,alprazolam,buspirone,etc.) 5=Mood stabilizers (e.g., lithium, valproate,lamotrigine,carbamazepine,etc.) 6=Sleep medications (e.g., zolpidem,zaleplon,etc.) 7=Others  8=No, none of these [mutually exclusive] 9=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
@@ -5617,7 +5613,7 @@
       </c>
       <c r="C44" s="2" t="inlineStr">
         <is>
-          <t>Which of the following are important reasons why you received the counselling services? (Select all that apply)</t>
+          <t>Which of the following are important reasons why you received those services? (Select all that apply)</t>
         </is>
       </c>
       <c r="D44" s="2" t="inlineStr">
@@ -6594,7 +6590,7 @@
       <c r="E3" s="2" t="inlineStr"/>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>1=Diabetes 2=High blood pressure 3=Asthma 4=Thyroid disease (e.g., hypothyroid or hyperthyroid) 5=Gastrointestinal disease (e.g., Crohn’s Disease, Ulcerative Colitis) 6=Arthritis 7=Sickle cell anemia 8=Seizure disorders (e.g., epilepsy) 9=Cancers 10=High cholesterol 11=HIV/AIDS 12=Other autoimmune disorder  13=Other chronic disease  14=No, never been diagnosed with a chronic disease. [mutually exclusive] 15=Don’t know [mutually exclusive]</t>
+          <t>1=Diabetes 2=High blood pressure 3=Asthma 4=Thyroid disease (e.g., hypothyroid or hyperthyroid) 5=Gastrointestinal disease (e.g., Crohn’s Disease, Ulcerative Colitis) 6=Arthritis 7=Sickle cell anemia 8=Seizure disorders (e.g., epilepsy) 9=Cancers 10=High cholesterol 11=HIV/AIDS 12=Other autoimmune disorder  13=Other chronic disease  14=No, never been diagnosed with a chronic disease. [mutually exclusive] 15=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -6864,7 +6860,7 @@
       <c r="E7" s="2" t="inlineStr"/>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0=No 1=Yes 2=I don’t know 3=Prefer not to say</t>
+          <t>0=No 1=Yes 2=I Don't know [mutually exclusive] 3=Prefer not to say</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -6873,11 +6869,11 @@
         </is>
       </c>
       <c r="H7" s="2" t="n">
-        <v>77.33</v>
+        <v>67.77</v>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -6904,7 +6900,7 @@
         </is>
       </c>
       <c r="O7" s="2" t="n">
-        <v>0.212</v>
+        <v>0.231</v>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
@@ -6936,7 +6932,7 @@
       <c r="E8" s="2" t="inlineStr"/>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0=No 1=Yes 2=I don’t know 3=Prefer not to say</t>
+          <t>0=No 1=Yes 2=I Don't know [mutually exclusive] 3=Prefer not to say</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6945,11 +6941,11 @@
         </is>
       </c>
       <c r="H8" s="2" t="n">
-        <v>75.44</v>
+        <v>67.16</v>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Moderate</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6976,7 +6972,7 @@
         </is>
       </c>
       <c r="O8" s="2" t="n">
-        <v>0.216</v>
+        <v>0.232</v>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
@@ -7066,7 +7062,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>1=Less than 5 minutes 2=Between 5 and 30 minutes 3=More than 30 minutes but less than 24 hours 4=24 hours or longer 5=I don’t know 6=Prefer not to say</t>
+          <t>1=Less than 5 minutes 2=Between 5 and 30 minutes 3=More than 30 minutes but less than 24 hours 4=24 hours or longer 5=I Don't know [mutually exclusive] 6=Prefer not to say</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8237,7 +8233,7 @@
       <c r="E9" s="2" t="inlineStr"/>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>1=2-year college degree (associate’s) 2=4-year college degree (bachelor’s) 3=Master’s degree 4=Doctoral degree (JD, MD, Ph D, etc.) 5=Other degree  6=Don’t know</t>
+          <t>1=2-year college degree (associate’s) 2=4-year college degree (bachelor’s) 3=Master’s degree 4=Doctoral degree (JD, MD, Ph D, etc.) 5=Other degree  6=Don't know [mutually exclusive]</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8246,7 +8242,7 @@
         </is>
       </c>
       <c r="H9" s="2" t="n">
-        <v>68.31999999999999</v>
+        <v>59.53</v>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
@@ -8277,7 +8273,7 @@
         </is>
       </c>
       <c r="O9" s="2" t="n">
-        <v>0.063</v>
+        <v>0.081</v>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -4785,7 +4785,7 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>How satisfied/dissatisfied are you with the following aspects of your therapy or counseling that you received in the past 12 months at [pipe in selected options from: “From which of the following places did you receive counseling or therapy?”]? Convenient hours Location [Do not display for digital resources] Quality of therapists/counselors Respect for my privacy concerns Ability to schedule appointments without long delays Respect and consideration for my identities (e.g., race/ethnicity, gender, etc.)</t>
+          <t>How satisfied/dissatisfied are you with the following aspects of your therapy or counseling that you received in the past 12 months at [pipe in selected options from: “From which of the following places did you receive counseling or therapy?”]? Convenient hours Location [Do not display for digital resources] Quality of therapists/counselors Respect for my privacy concerns Ability to schedule appointments without long delays Respect and consideration for my beliefs (e.g., faith, gender, etc.)</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F44" s="2" t="inlineStr">
         <is>
-          <t>1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help  7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help 8=I acquired more information about my options from  10= A health professional recommended or referred me to seek help. 12=Others</t>
+          <t>1=I decided on my own to seek help. 2=A friend encouraged me to seek help. 3=A friend pressured me to seek help. 4=A family member encouraged me to seek help. 5=A family member pressured me to seek help. 6=Someone other than a friend or family member encouraged me to seek help  7= A campus advisor mandated me to seek help 11= A campus advisor referred me to seek help  10= A health professional recommended or referred me to seek help. 12=Others</t>
         </is>
       </c>
       <c r="G44" s="2" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -1627,7 +1627,12 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>Please answer the following questions as honestly as possible. 1. Do you often feel the desire to eat when you are emotionally upset or stressed? 2. Do you often feel that you can't control what or how much you eat? 3. Do you sometimes make yourself throw up (vomit) to control your weight? 4. Are you often preoccupied with a desire to be thinner? 5. Do you believe yourself to be fat when others say you are thin?</t>
+          <t>Please answer the following questions as honestly as possible.
+1. Do you often feel the desire to eat when you are emotionally upset or stressed?
+2. Do you often feel that you can't control what or how much you eat?
+3. Do you sometimes make yourself throw up (vomit) to control your weight?
+4. Are you often preoccupied with a desire to be thinner?
+5. Do you believe yourself to be fat when others say you are thin?</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
@@ -3001,7 +3006,7 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>We know that there are many experiences in the online space, ranging from positive to neutral to negative. For this item, we want to know more about your negative online experiences. Please select all the negative experiences you have had in online spaces (such as social media) in the past year.</t>
+          <t>We know that there are many experiences in the online space, ranging from positive to neutral to negative. For this item, we want to know more about your negative online experiences. Please select all the negative experiences you have had in online spaces (such as social media) in the past year. (Select all that apply)</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -1795,7 +1795,7 @@
       <c r="E12" s="2" t="inlineStr"/>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1=Cut myself 2=Burned myself 3=Punched or banged myself 4=Scratched myself 5=Pulled my hair 6=Bit myself 7=Interfered with wound healing 8=Carved words or symbols into skin 9=Rubbed sharp objects into skin 10=Punched or banged an object to hurt myself 11=Other (please specify) 12=No, none of these [mutually exclusive]</t>
+          <t>1=Cut myself 2=Burned myself 3=Punched or banged myself 4=Scratched myself 5=Pulled my hair 6=Bit myself 7=Interfered with wound healing 8=Carved words or symbols into skin 9=Rubbed sharp objects into skin 10=Punched or banged an object to hurt myself 11=Others 12=No, none of these [mutually exclusive]</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="H12" s="2" t="n">
-        <v>59.75</v>
+        <v>61.88</v>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
@@ -1835,7 +1835,7 @@
         </is>
       </c>
       <c r="O12" s="2" t="n">
-        <v>0.481</v>
+        <v>0.476</v>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -1622,7 +1622,7 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SDE</t>
+          <t>Eating and body image</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">

--- a/SurveyQuestions/outputs/hms_question_score.xlsx
+++ b/SurveyQuestions/outputs/hms_question_score.xlsx
@@ -2779,7 +2779,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>1=An official institutional communication (e.g., email, emergency alert system) 2=A memorial 3=News media (e.g., newspapers or blogs) 4=Social media (e.g., Reddit, Instagram, Meta, X) 5=Word of mouth from my peers 6=Others  7=I don’t remember [mutually exclusive] 8=None of these</t>
+          <t>1=An official institutional communication (e.g., email, emergency alert system) 2=A memorial 3=News media (e.g., newspapers or blogs) 4=Social media (e.g., Reddit, Instagram, Meta, X) 5=Word of mouth from my peers 6=Others  7=I don’t remember [mutually exclusive] 8=None of these [mutually exclusive]</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
